--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MISSISSIPPI_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MISSISSIPPI_2018.xlsx
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C83">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C162">
@@ -9211,7 +9211,7 @@
         <v>18</v>
       </c>
       <c r="D492">
-        <v>0.009350649350649351</v>
+        <v>0.009350649350649352</v>
       </c>
     </row>
     <row r="493">
